--- a/Proyecto/PREGAME/1. ELICITACION/1.3 Historias de Usuario/Gn6ºMatriz de Marco de Trabajo HU_V.1.xlsx
+++ b/Proyecto/PREGAME/1. ELICITACION/1.3 Historias de Usuario/Gn6ºMatriz de Marco de Trabajo HU_V.1.xlsx
@@ -8,16 +8,16 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Jesocasi\Desktop\mtodologia\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6E2B13EB-D512-47C8-99A6-015FD2357046}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{112855E0-8260-435B-BB0A-430FF2F6CAFA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Formato descripción HU" sheetId="1" r:id="rId1"/>
     <sheet name="Historia de Usuario" sheetId="2" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm.Print_Area" localSheetId="0">'Formato descripción HU'!$B$3:$O$13</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="0">'Formato descripción HU'!$B$3:$O$14</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="1">'Historia de Usuario'!$B$1:$P$25</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
@@ -31,15 +31,12 @@
         <xcalcf:feature name="microsoft.com:LET_WF"/>
       </xcalcf:calcFeatures>
     </ext>
-    <ext uri="GoogleSheetsCustomDataVersion2">
-      <go:sheetsCustomData xmlns:go="http://customooxmlschemas.google.com/" r:id="rId6" roundtripDataChecksum="DNGkBTMA7r/+PxmOhB9lRm6CfgtH2Hn0zJgcueEAPYk="/>
-    </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="102" uniqueCount="76">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="115" uniqueCount="85">
   <si>
     <t>Matriz de Marco de Trabajo de HU</t>
   </si>
@@ -272,6 +269,33 @@
   <si>
     <t>Actua como una forma de comunicacion directa entre el cliente y el negocio registrando los datos del cliente y su pedido.</t>
   </si>
+  <si>
+    <t>REQ006</t>
+  </si>
+  <si>
+    <t>No hay control de acceso ni validación de usuarios</t>
+  </si>
+  <si>
+    <t>Implementar inicio de sesión con usuario y contraseña</t>
+  </si>
+  <si>
+    <t>Crear módulo de login con campos: usuario, contraseña; validación contra base de datos; mensajes de error; redirección según rol</t>
+  </si>
+  <si>
+    <t>Para controlar el acceso y el flujo de personas</t>
+  </si>
+  <si>
+    <t>Administradora y Cliente</t>
+  </si>
+  <si>
+    <t>Se ingresa usuario y contraseña válidos y se accede al sistema;  usuario y contraseña incorrectas muestran error</t>
+  </si>
+  <si>
+    <t>Validar acceso correcto, errores por usuario y contraseña inválidas y redirección por rol</t>
+  </si>
+  <si>
+    <t>Inicio de sesión con usuario y contraseña</t>
+  </si>
 </sst>
 </file>
 
@@ -281,11 +305,18 @@
     <numFmt numFmtId="164" formatCode="d/mm/yyyy"/>
     <numFmt numFmtId="165" formatCode="yyyy\-mm\-dd"/>
   </numFmts>
-  <fonts count="20" x14ac:knownFonts="1">
+  <fonts count="21" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Arial"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Arial"/>
+      <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -790,273 +821,308 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="5"/>
   </cellStyleXfs>
-  <cellXfs count="110">
+  <cellXfs count="121">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="5" fillId="3" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="6" fillId="3" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="5" fillId="3" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="6" fillId="3" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="165" fontId="5" fillId="3" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="6" fillId="3" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="4" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="4" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="5" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="9" fillId="5" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="5" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="10" fillId="5" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="5" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="6" fillId="5" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="6" fillId="5" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="6" fillId="5" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="12" fillId="6" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="5" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="7" fillId="5" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="7" fillId="5" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="7" fillId="5" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="13" fillId="6" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="5" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="14" fillId="5" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="5" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="6" fillId="5" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="14" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="5" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="7" fillId="5" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="15" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="5" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="5" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="5" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="5" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="5" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="15" fillId="5" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="5" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="5" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="5" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="5" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="5" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="6" fillId="5" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="6" fillId="5" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
+    <xf numFmtId="0" fontId="7" fillId="5" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="7" fillId="5" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="7" fillId="5" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="49" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="19" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="20" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="19" fillId="3" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="20" fillId="3" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="20" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="3" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="6" fillId="3" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="11" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="10" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="13" fillId="6" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="49" fontId="11" fillId="3" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="11" fillId="3" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="7" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="6" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="15" fillId="2" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="49" fontId="10" fillId="3" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="16" fillId="8" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="10" fillId="3" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="13" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="11" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="7" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="10" fillId="3" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="2" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="15" fillId="8" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="10" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="49" fontId="10" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="49" fontId="11" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="16" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="17" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="11" fillId="3" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="4" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="6" fillId="3" borderId="4" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="4" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="2">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="Normal 2" xfId="1" xr:uid="{5A0829D0-E586-4D13-9F91-F431C5419386}"/>
   </cellStyles>
   <dxfs count="4">
     <dxf>
@@ -1417,7 +1483,7 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:Z1003"/>
+  <dimension ref="A1:Z1004"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="12.75" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="4.75" customWidth="1"/>
@@ -1491,22 +1557,22 @@
     </row>
     <row r="3" spans="1:26" ht="45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3" s="1"/>
-      <c r="B3" s="109" t="s">
+      <c r="B3" s="108" t="s">
         <v>0</v>
       </c>
-      <c r="C3" s="98"/>
-      <c r="D3" s="98"/>
-      <c r="E3" s="98"/>
-      <c r="F3" s="98"/>
-      <c r="G3" s="98"/>
-      <c r="H3" s="98"/>
-      <c r="I3" s="98"/>
-      <c r="J3" s="98"/>
-      <c r="K3" s="98"/>
-      <c r="L3" s="98"/>
-      <c r="M3" s="98"/>
-      <c r="N3" s="98"/>
-      <c r="O3" s="95"/>
+      <c r="C3" s="97"/>
+      <c r="D3" s="97"/>
+      <c r="E3" s="97"/>
+      <c r="F3" s="97"/>
+      <c r="G3" s="97"/>
+      <c r="H3" s="97"/>
+      <c r="I3" s="97"/>
+      <c r="J3" s="97"/>
+      <c r="K3" s="97"/>
+      <c r="L3" s="97"/>
+      <c r="M3" s="97"/>
+      <c r="N3" s="97"/>
+      <c r="O3" s="94"/>
       <c r="P3" s="1"/>
       <c r="Q3" s="1"/>
       <c r="R3" s="1"/>
@@ -1608,44 +1674,44 @@
       <c r="B6" s="6" t="s">
         <v>15</v>
       </c>
-      <c r="C6" s="6" t="s">
-        <v>40</v>
+      <c r="C6" s="118" t="s">
+        <v>77</v>
       </c>
-      <c r="D6" s="6" t="s">
-        <v>41</v>
+      <c r="D6" s="118" t="s">
+        <v>78</v>
       </c>
-      <c r="E6" s="6" t="s">
-        <v>69</v>
+      <c r="E6" s="118" t="s">
+        <v>80</v>
       </c>
-      <c r="F6" s="6" t="s">
-        <v>62</v>
+      <c r="F6" s="118" t="s">
+        <v>81</v>
       </c>
-      <c r="G6" s="6" t="s">
-        <v>51</v>
+      <c r="G6" s="118" t="s">
+        <v>79</v>
       </c>
-      <c r="H6" s="6" t="s">
-        <v>38</v>
+      <c r="H6" s="118" t="s">
+        <v>39</v>
       </c>
-      <c r="I6" s="6">
+      <c r="I6" s="118">
         <v>6</v>
       </c>
       <c r="J6" s="59" t="s">
         <v>37</v>
       </c>
-      <c r="K6" s="6" t="s">
+      <c r="K6" s="118" t="s">
         <v>16</v>
       </c>
-      <c r="L6" s="6" t="s">
+      <c r="L6" s="118" t="s">
         <v>21</v>
       </c>
-      <c r="M6" s="7" t="s">
-        <v>64</v>
+      <c r="M6" s="119" t="s">
+        <v>82</v>
       </c>
-      <c r="N6" s="6" t="s">
-        <v>73</v>
+      <c r="N6" s="118" t="s">
+        <v>83</v>
       </c>
-      <c r="O6" s="8" t="s">
-        <v>63</v>
+      <c r="O6" s="120" t="s">
+        <v>84</v>
       </c>
       <c r="P6" s="9"/>
       <c r="Q6" s="9"/>
@@ -1665,25 +1731,25 @@
         <v>18</v>
       </c>
       <c r="C7" s="6" t="s">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="D7" s="6" t="s">
-        <v>45</v>
+        <v>41</v>
       </c>
       <c r="E7" s="6" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="F7" s="6" t="s">
         <v>62</v>
       </c>
       <c r="G7" s="6" t="s">
-        <v>66</v>
+        <v>51</v>
       </c>
       <c r="H7" s="6" t="s">
         <v>38</v>
       </c>
       <c r="I7" s="6">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="J7" s="59" t="s">
         <v>37</v>
@@ -1695,13 +1761,13 @@
         <v>21</v>
       </c>
       <c r="M7" s="7" t="s">
-        <v>53</v>
+        <v>64</v>
       </c>
       <c r="N7" s="6" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="O7" s="8" t="s">
-        <v>57</v>
+        <v>63</v>
       </c>
       <c r="P7" s="9"/>
       <c r="Q7" s="9"/>
@@ -1721,25 +1787,25 @@
         <v>19</v>
       </c>
       <c r="C8" s="6" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="D8" s="6" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="E8" s="6" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="F8" s="6" t="s">
         <v>62</v>
       </c>
       <c r="G8" s="6" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="H8" s="6" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="I8" s="6">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="J8" s="59" t="s">
         <v>37</v>
@@ -1751,13 +1817,13 @@
         <v>21</v>
       </c>
       <c r="M8" s="7" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="N8" s="6" t="s">
-        <v>60</v>
+        <v>74</v>
       </c>
       <c r="O8" s="8" t="s">
-        <v>65</v>
+        <v>57</v>
       </c>
       <c r="P8" s="9"/>
       <c r="Q8" s="9"/>
@@ -1777,25 +1843,25 @@
         <v>20</v>
       </c>
       <c r="C9" s="6" t="s">
-        <v>47</v>
+        <v>42</v>
       </c>
       <c r="D9" s="6" t="s">
-        <v>48</v>
+        <v>43</v>
       </c>
       <c r="E9" s="6" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="F9" s="6" t="s">
         <v>62</v>
       </c>
       <c r="G9" s="6" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="H9" s="6" t="s">
         <v>39</v>
       </c>
       <c r="I9" s="6">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="J9" s="59" t="s">
         <v>37</v>
@@ -1807,13 +1873,13 @@
         <v>21</v>
       </c>
       <c r="M9" s="7" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="N9" s="6" t="s">
-        <v>75</v>
+        <v>60</v>
       </c>
       <c r="O9" s="8" t="s">
-        <v>58</v>
+        <v>65</v>
       </c>
       <c r="P9" s="1"/>
       <c r="Q9" s="1"/>
@@ -1833,22 +1899,22 @@
         <v>22</v>
       </c>
       <c r="C10" s="6" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
-      <c r="D10" s="60" t="s">
-        <v>49</v>
+      <c r="D10" s="6" t="s">
+        <v>48</v>
       </c>
       <c r="E10" s="6" t="s">
-        <v>50</v>
+        <v>72</v>
       </c>
       <c r="F10" s="6" t="s">
         <v>62</v>
       </c>
       <c r="G10" s="6" t="s">
-        <v>52</v>
+        <v>68</v>
       </c>
       <c r="H10" s="6" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="I10" s="6">
         <v>4</v>
@@ -1863,13 +1929,13 @@
         <v>21</v>
       </c>
       <c r="M10" s="7" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="N10" s="6" t="s">
-        <v>61</v>
+        <v>75</v>
       </c>
       <c r="O10" s="8" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="P10" s="1"/>
       <c r="Q10" s="1"/>
@@ -1885,20 +1951,48 @@
     </row>
     <row r="11" spans="1:26" ht="109.9" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A11" s="5"/>
-      <c r="B11" s="6"/>
-      <c r="C11" s="56"/>
-      <c r="D11" s="56"/>
-      <c r="E11" s="56"/>
-      <c r="F11" s="56"/>
-      <c r="G11" s="56"/>
-      <c r="H11" s="56"/>
-      <c r="I11" s="6"/>
-      <c r="J11" s="59"/>
-      <c r="K11" s="6"/>
-      <c r="L11" s="6"/>
-      <c r="M11" s="57"/>
-      <c r="N11" s="56"/>
-      <c r="O11" s="58"/>
+      <c r="B11" s="6" t="s">
+        <v>76</v>
+      </c>
+      <c r="C11" s="6" t="s">
+        <v>46</v>
+      </c>
+      <c r="D11" s="60" t="s">
+        <v>49</v>
+      </c>
+      <c r="E11" s="6" t="s">
+        <v>50</v>
+      </c>
+      <c r="F11" s="6" t="s">
+        <v>62</v>
+      </c>
+      <c r="G11" s="6" t="s">
+        <v>52</v>
+      </c>
+      <c r="H11" s="6" t="s">
+        <v>38</v>
+      </c>
+      <c r="I11" s="6">
+        <v>4</v>
+      </c>
+      <c r="J11" s="59" t="s">
+        <v>37</v>
+      </c>
+      <c r="K11" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="L11" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="M11" s="7" t="s">
+        <v>56</v>
+      </c>
+      <c r="N11" s="6" t="s">
+        <v>61</v>
+      </c>
+      <c r="O11" s="8" t="s">
+        <v>59</v>
+      </c>
       <c r="P11" s="1"/>
       <c r="Q11" s="1"/>
       <c r="R11" s="1"/>
@@ -1914,19 +2008,19 @@
     <row r="12" spans="1:26" ht="109.9" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A12" s="5"/>
       <c r="B12" s="6"/>
-      <c r="C12" s="6"/>
-      <c r="D12" s="11"/>
-      <c r="E12" s="6"/>
-      <c r="F12" s="6"/>
-      <c r="G12" s="11"/>
-      <c r="H12" s="6"/>
+      <c r="C12" s="56"/>
+      <c r="D12" s="56"/>
+      <c r="E12" s="56"/>
+      <c r="F12" s="56"/>
+      <c r="G12" s="56"/>
+      <c r="H12" s="56"/>
       <c r="I12" s="6"/>
-      <c r="J12" s="10"/>
+      <c r="J12" s="59"/>
       <c r="K12" s="6"/>
       <c r="L12" s="6"/>
-      <c r="M12" s="6"/>
-      <c r="N12" s="6"/>
-      <c r="O12" s="12"/>
+      <c r="M12" s="57"/>
+      <c r="N12" s="56"/>
+      <c r="O12" s="58"/>
       <c r="P12" s="1"/>
       <c r="Q12" s="1"/>
       <c r="R12" s="1"/>
@@ -1969,6 +2063,20 @@
     </row>
     <row r="14" spans="1:26" ht="70.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A14" s="5"/>
+      <c r="B14" s="6"/>
+      <c r="C14" s="6"/>
+      <c r="D14" s="11"/>
+      <c r="E14" s="6"/>
+      <c r="F14" s="6"/>
+      <c r="G14" s="11"/>
+      <c r="H14" s="6"/>
+      <c r="I14" s="6"/>
+      <c r="J14" s="10"/>
+      <c r="K14" s="6"/>
+      <c r="L14" s="6"/>
+      <c r="M14" s="6"/>
+      <c r="N14" s="6"/>
+      <c r="O14" s="12"/>
       <c r="P14" s="1"/>
       <c r="Q14" s="1"/>
       <c r="R14" s="1"/>
@@ -1983,20 +2091,6 @@
     </row>
     <row r="15" spans="1:26" ht="61.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A15" s="5"/>
-      <c r="B15" s="5"/>
-      <c r="C15" s="5"/>
-      <c r="D15" s="5"/>
-      <c r="E15" s="5"/>
-      <c r="F15" s="5"/>
-      <c r="G15" s="5"/>
-      <c r="H15" s="5"/>
-      <c r="I15" s="5"/>
-      <c r="J15" s="5"/>
-      <c r="K15" s="5"/>
-      <c r="L15" s="5"/>
-      <c r="M15" s="5"/>
-      <c r="N15" s="5"/>
-      <c r="O15" s="1"/>
       <c r="P15" s="1"/>
       <c r="Q15" s="1"/>
       <c r="R15" s="1"/>
@@ -2067,20 +2161,20 @@
     </row>
     <row r="18" spans="1:26" ht="39.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A18" s="5"/>
-      <c r="B18" s="13"/>
-      <c r="C18" s="14"/>
-      <c r="D18" s="14"/>
+      <c r="B18" s="5"/>
+      <c r="C18" s="5"/>
+      <c r="D18" s="5"/>
       <c r="E18" s="5"/>
-      <c r="F18" s="14"/>
-      <c r="G18" s="14"/>
-      <c r="H18" s="14"/>
-      <c r="I18" s="15"/>
-      <c r="J18" s="16"/>
-      <c r="K18" s="15"/>
-      <c r="L18" s="15"/>
-      <c r="M18" s="14"/>
-      <c r="N18" s="14"/>
-      <c r="O18" s="17"/>
+      <c r="F18" s="5"/>
+      <c r="G18" s="5"/>
+      <c r="H18" s="5"/>
+      <c r="I18" s="5"/>
+      <c r="J18" s="5"/>
+      <c r="K18" s="5"/>
+      <c r="L18" s="5"/>
+      <c r="M18" s="5"/>
+      <c r="N18" s="5"/>
+      <c r="O18" s="1"/>
       <c r="P18" s="1"/>
       <c r="Q18" s="1"/>
       <c r="R18" s="1"/>
@@ -2098,7 +2192,7 @@
       <c r="B19" s="13"/>
       <c r="C19" s="14"/>
       <c r="D19" s="14"/>
-      <c r="E19" s="14"/>
+      <c r="E19" s="5"/>
       <c r="F19" s="14"/>
       <c r="G19" s="14"/>
       <c r="H19" s="14"/>
@@ -2107,7 +2201,7 @@
       <c r="K19" s="15"/>
       <c r="L19" s="15"/>
       <c r="M19" s="14"/>
-      <c r="N19" s="18"/>
+      <c r="N19" s="14"/>
       <c r="O19" s="17"/>
       <c r="P19" s="1"/>
       <c r="Q19" s="1"/>
@@ -2126,7 +2220,7 @@
       <c r="B20" s="13"/>
       <c r="C20" s="14"/>
       <c r="D20" s="14"/>
-      <c r="E20" s="5"/>
+      <c r="E20" s="14"/>
       <c r="F20" s="14"/>
       <c r="G20" s="14"/>
       <c r="H20" s="14"/>
@@ -2135,7 +2229,7 @@
       <c r="K20" s="15"/>
       <c r="L20" s="15"/>
       <c r="M20" s="14"/>
-      <c r="N20" s="14"/>
+      <c r="N20" s="18"/>
       <c r="O20" s="17"/>
       <c r="P20" s="1"/>
       <c r="Q20" s="1"/>
@@ -2154,7 +2248,7 @@
       <c r="B21" s="13"/>
       <c r="C21" s="14"/>
       <c r="D21" s="14"/>
-      <c r="E21" s="14"/>
+      <c r="E21" s="5"/>
       <c r="F21" s="14"/>
       <c r="G21" s="14"/>
       <c r="H21" s="14"/>
@@ -2162,7 +2256,7 @@
       <c r="J21" s="16"/>
       <c r="K21" s="15"/>
       <c r="L21" s="15"/>
-      <c r="M21" s="18"/>
+      <c r="M21" s="14"/>
       <c r="N21" s="14"/>
       <c r="O21" s="17"/>
       <c r="P21" s="1"/>
@@ -2190,11 +2284,9 @@
       <c r="J22" s="16"/>
       <c r="K22" s="15"/>
       <c r="L22" s="15"/>
-      <c r="M22" s="14" t="s">
-        <v>24</v>
-      </c>
+      <c r="M22" s="18"/>
       <c r="N22" s="14"/>
-      <c r="O22" s="19"/>
+      <c r="O22" s="17"/>
       <c r="P22" s="1"/>
       <c r="Q22" s="1"/>
       <c r="R22" s="1"/>
@@ -2209,20 +2301,22 @@
     </row>
     <row r="23" spans="1:26" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A23" s="5"/>
-      <c r="B23" s="5"/>
-      <c r="C23" s="5"/>
-      <c r="D23" s="5"/>
-      <c r="E23" s="5"/>
-      <c r="F23" s="5"/>
-      <c r="G23" s="5"/>
-      <c r="H23" s="5"/>
-      <c r="I23" s="20"/>
-      <c r="J23" s="20"/>
-      <c r="K23" s="21"/>
-      <c r="L23" s="20"/>
-      <c r="M23" s="5"/>
-      <c r="N23" s="5"/>
-      <c r="O23" s="1"/>
+      <c r="B23" s="13"/>
+      <c r="C23" s="14"/>
+      <c r="D23" s="14"/>
+      <c r="E23" s="14"/>
+      <c r="F23" s="14"/>
+      <c r="G23" s="14"/>
+      <c r="H23" s="14"/>
+      <c r="I23" s="15"/>
+      <c r="J23" s="16"/>
+      <c r="K23" s="15"/>
+      <c r="L23" s="15"/>
+      <c r="M23" s="14" t="s">
+        <v>24</v>
+      </c>
+      <c r="N23" s="14"/>
+      <c r="O23" s="19"/>
       <c r="P23" s="1"/>
       <c r="Q23" s="1"/>
       <c r="R23" s="1"/>
@@ -2271,7 +2365,7 @@
       <c r="E25" s="5"/>
       <c r="F25" s="5"/>
       <c r="G25" s="5"/>
-      <c r="H25" s="18"/>
+      <c r="H25" s="5"/>
       <c r="I25" s="20"/>
       <c r="J25" s="20"/>
       <c r="K25" s="21"/>
@@ -2299,7 +2393,7 @@
       <c r="E26" s="5"/>
       <c r="F26" s="5"/>
       <c r="G26" s="5"/>
-      <c r="H26" s="5"/>
+      <c r="H26" s="18"/>
       <c r="I26" s="20"/>
       <c r="J26" s="20"/>
       <c r="K26" s="21"/>
@@ -2330,7 +2424,7 @@
       <c r="H27" s="5"/>
       <c r="I27" s="20"/>
       <c r="J27" s="20"/>
-      <c r="K27" s="22"/>
+      <c r="K27" s="21"/>
       <c r="L27" s="20"/>
       <c r="M27" s="5"/>
       <c r="N27" s="5"/>
@@ -2386,7 +2480,7 @@
       <c r="H29" s="5"/>
       <c r="I29" s="20"/>
       <c r="J29" s="20"/>
-      <c r="K29" s="21"/>
+      <c r="K29" s="22"/>
       <c r="L29" s="20"/>
       <c r="M29" s="5"/>
       <c r="N29" s="5"/>
@@ -2413,9 +2507,9 @@
       <c r="G30" s="5"/>
       <c r="H30" s="5"/>
       <c r="I30" s="20"/>
-      <c r="J30" s="5"/>
-      <c r="K30" s="5"/>
-      <c r="L30" s="5"/>
+      <c r="J30" s="20"/>
+      <c r="K30" s="21"/>
+      <c r="L30" s="20"/>
       <c r="M30" s="5"/>
       <c r="N30" s="5"/>
       <c r="O30" s="1"/>
@@ -2470,12 +2564,8 @@
       <c r="H32" s="5"/>
       <c r="I32" s="20"/>
       <c r="J32" s="5"/>
-      <c r="K32" s="21" t="s">
-        <v>16</v>
-      </c>
-      <c r="L32" s="21" t="s">
-        <v>21</v>
-      </c>
+      <c r="K32" s="5"/>
+      <c r="L32" s="5"/>
       <c r="M32" s="5"/>
       <c r="N32" s="5"/>
       <c r="O32" s="1"/>
@@ -2503,10 +2593,10 @@
       <c r="I33" s="20"/>
       <c r="J33" s="5"/>
       <c r="K33" s="21" t="s">
-        <v>23</v>
+        <v>16</v>
       </c>
       <c r="L33" s="21" t="s">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="M33" s="5"/>
       <c r="N33" s="5"/>
@@ -2535,10 +2625,10 @@
       <c r="I34" s="20"/>
       <c r="J34" s="5"/>
       <c r="K34" s="21" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="L34" s="21" t="s">
-        <v>26</v>
+        <v>17</v>
       </c>
       <c r="M34" s="5"/>
       <c r="N34" s="5"/>
@@ -2566,9 +2656,11 @@
       <c r="H35" s="5"/>
       <c r="I35" s="20"/>
       <c r="J35" s="5"/>
-      <c r="K35" s="21"/>
+      <c r="K35" s="21" t="s">
+        <v>25</v>
+      </c>
       <c r="L35" s="21" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="M35" s="5"/>
       <c r="N35" s="5"/>
@@ -2596,8 +2688,10 @@
       <c r="H36" s="5"/>
       <c r="I36" s="20"/>
       <c r="J36" s="5"/>
-      <c r="K36" s="5"/>
-      <c r="L36" s="5"/>
+      <c r="K36" s="21"/>
+      <c r="L36" s="21" t="s">
+        <v>27</v>
+      </c>
       <c r="M36" s="5"/>
       <c r="N36" s="5"/>
       <c r="O36" s="1"/>
@@ -2707,9 +2801,9 @@
       <c r="G40" s="5"/>
       <c r="H40" s="5"/>
       <c r="I40" s="20"/>
-      <c r="J40" s="20"/>
-      <c r="K40" s="21"/>
-      <c r="L40" s="20"/>
+      <c r="J40" s="5"/>
+      <c r="K40" s="5"/>
+      <c r="L40" s="5"/>
       <c r="M40" s="5"/>
       <c r="N40" s="5"/>
       <c r="O40" s="1"/>
@@ -29689,11 +29783,27 @@
       <c r="Y1003" s="1"/>
       <c r="Z1003" s="1"/>
     </row>
+    <row r="1004" spans="1:26" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B1004" s="5"/>
+      <c r="C1004" s="5"/>
+      <c r="D1004" s="5"/>
+      <c r="E1004" s="5"/>
+      <c r="F1004" s="5"/>
+      <c r="G1004" s="5"/>
+      <c r="H1004" s="5"/>
+      <c r="I1004" s="20"/>
+      <c r="J1004" s="20"/>
+      <c r="K1004" s="21"/>
+      <c r="L1004" s="20"/>
+      <c r="M1004" s="5"/>
+      <c r="N1004" s="5"/>
+      <c r="O1004" s="1"/>
+    </row>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="B3:O3"/>
   </mergeCells>
-  <conditionalFormatting sqref="K6:K9">
+  <conditionalFormatting sqref="K7:K10">
     <cfRule type="colorScale" priority="2">
       <colorScale>
         <cfvo type="min"/>
@@ -29703,7 +29813,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="L6:L14">
+  <conditionalFormatting sqref="L7:L15">
     <cfRule type="colorScale" priority="3">
       <colorScale>
         <cfvo type="min"/>
@@ -29713,7 +29823,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="L9">
+  <conditionalFormatting sqref="L10">
     <cfRule type="colorScale" priority="4">
       <colorScale>
         <cfvo type="min"/>
@@ -29723,7 +29833,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="L10">
+  <conditionalFormatting sqref="L11">
     <cfRule type="colorScale" priority="1">
       <colorScale>
         <cfvo type="min"/>
@@ -29733,7 +29843,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="L12">
+  <conditionalFormatting sqref="L13">
     <cfRule type="colorScale" priority="5">
       <colorScale>
         <cfvo type="min"/>
@@ -29744,16 +29854,16 @@
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="4">
-    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="L6:L13" xr:uid="{00000000-0002-0000-0000-000000000000}">
-      <formula1>$L$32:$L$35</formula1>
+    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="L7:L14" xr:uid="{00000000-0002-0000-0000-000000000000}">
+      <formula1>$L$33:$L$36</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="K6:K13" xr:uid="{00000000-0002-0000-0000-000001000000}">
-      <formula1>$K$32:$K$34</formula1>
+    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="K7:K14" xr:uid="{00000000-0002-0000-0000-000001000000}">
+      <formula1>$K$33:$K$35</formula1>
     </dataValidation>
-    <dataValidation type="custom" allowBlank="1" showDropDown="1" sqref="J6:J13" xr:uid="{00000000-0002-0000-0000-000002000000}">
+    <dataValidation type="custom" allowBlank="1" showDropDown="1" sqref="J6:J14" xr:uid="{00000000-0002-0000-0000-000002000000}">
       <formula1>OR(NOT(ISERROR(DATEVALUE(J6))), AND(ISNUMBER(J6), LEFT(CELL("format", J6))="D"))</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="K15:L22" xr:uid="{00000000-0002-0000-0000-000003000000}">
+    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="K16:L23" xr:uid="{00000000-0002-0000-0000-000003000000}">
       <formula1>#REF!</formula1>
     </dataValidation>
   </dataValidations>
@@ -29793,23 +29903,23 @@
       <c r="F5" s="24"/>
     </row>
     <row r="6" spans="1:26" ht="39.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B6" s="97" t="s">
+      <c r="B6" s="96" t="s">
         <v>28</v>
       </c>
-      <c r="C6" s="98"/>
-      <c r="D6" s="98"/>
-      <c r="E6" s="98"/>
-      <c r="F6" s="98"/>
-      <c r="G6" s="98"/>
-      <c r="H6" s="98"/>
-      <c r="I6" s="98"/>
-      <c r="J6" s="98"/>
-      <c r="K6" s="98"/>
-      <c r="L6" s="98"/>
-      <c r="M6" s="98"/>
-      <c r="N6" s="98"/>
-      <c r="O6" s="98"/>
-      <c r="P6" s="95"/>
+      <c r="C6" s="97"/>
+      <c r="D6" s="97"/>
+      <c r="E6" s="97"/>
+      <c r="F6" s="97"/>
+      <c r="G6" s="97"/>
+      <c r="H6" s="97"/>
+      <c r="I6" s="97"/>
+      <c r="J6" s="97"/>
+      <c r="K6" s="97"/>
+      <c r="L6" s="97"/>
+      <c r="M6" s="97"/>
+      <c r="N6" s="97"/>
+      <c r="O6" s="97"/>
+      <c r="P6" s="94"/>
     </row>
     <row r="7" spans="1:26" ht="9.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A7" s="25"/>
@@ -29863,15 +29973,15 @@
         <v>1</v>
       </c>
       <c r="D9" s="34"/>
-      <c r="E9" s="94" t="s">
+      <c r="E9" s="93" t="s">
         <v>29</v>
       </c>
-      <c r="F9" s="95"/>
+      <c r="F9" s="94"/>
       <c r="G9" s="34"/>
-      <c r="H9" s="94" t="s">
+      <c r="H9" s="93" t="s">
         <v>11</v>
       </c>
-      <c r="I9" s="95"/>
+      <c r="I9" s="94"/>
       <c r="J9" s="35"/>
       <c r="K9" s="35"/>
       <c r="L9" s="35"/>
@@ -29887,17 +29997,17 @@
         <v>22</v>
       </c>
       <c r="D10" s="38"/>
-      <c r="E10" s="96" t="str">
-        <f>VLOOKUP(C10,'Formato descripción HU'!B6:O22,5,0)</f>
+      <c r="E10" s="95" t="str">
+        <f>VLOOKUP(C10,'Formato descripción HU'!B7:O23,5,0)</f>
         <v>Administrador y Cliente</v>
       </c>
-      <c r="F10" s="95"/>
+      <c r="F10" s="94"/>
       <c r="G10" s="39"/>
-      <c r="H10" s="96" t="str">
-        <f>VLOOKUP(C10,'Formato descripción HU'!B6:O22,11,0)</f>
+      <c r="H10" s="95" t="str">
+        <f>VLOOKUP(C10,'Formato descripción HU'!B7:O23,11,0)</f>
         <v>No iniciado</v>
       </c>
-      <c r="I10" s="95"/>
+      <c r="I10" s="94"/>
       <c r="J10" s="39"/>
       <c r="K10" s="35"/>
       <c r="L10" s="35"/>
@@ -29941,15 +30051,15 @@
         <v>30</v>
       </c>
       <c r="D12" s="38"/>
-      <c r="E12" s="94" t="s">
+      <c r="E12" s="93" t="s">
         <v>10</v>
       </c>
-      <c r="F12" s="95"/>
+      <c r="F12" s="94"/>
       <c r="G12" s="39"/>
-      <c r="H12" s="94" t="s">
+      <c r="H12" s="93" t="s">
         <v>31</v>
       </c>
-      <c r="I12" s="95"/>
+      <c r="I12" s="94"/>
       <c r="J12" s="39"/>
       <c r="K12" s="41"/>
       <c r="L12" s="41"/>
@@ -29972,21 +30082,21 @@
       <c r="A13" s="25"/>
       <c r="B13" s="32"/>
       <c r="C13" s="37">
-        <f>VLOOKUP('Historia de Usuario'!C10,'Formato descripción HU'!B6:O22,8,0)</f>
+        <f>VLOOKUP('Historia de Usuario'!C10,'Formato descripción HU'!B7:O23,8,0)</f>
         <v>4</v>
       </c>
       <c r="D13" s="38"/>
-      <c r="E13" s="96" t="str">
-        <f>VLOOKUP(C10,'Formato descripción HU'!B6:O22,10,0)</f>
+      <c r="E13" s="95" t="str">
+        <f>VLOOKUP(C10,'Formato descripción HU'!B7:O23,10,0)</f>
         <v>Alta</v>
       </c>
-      <c r="F13" s="95"/>
+      <c r="F13" s="94"/>
       <c r="G13" s="39"/>
-      <c r="H13" s="96" t="str">
-        <f>VLOOKUP(C10,'Formato descripción HU'!B6:O22,7,0)</f>
-        <v>Juan Socasi</v>
+      <c r="H13" s="95" t="str">
+        <f>VLOOKUP(C10,'Formato descripción HU'!B7:O23,7,0)</f>
+        <v>Vicente Sanchez</v>
       </c>
-      <c r="I13" s="95"/>
+      <c r="I13" s="94"/>
       <c r="J13" s="39"/>
       <c r="K13" s="41"/>
       <c r="L13" s="41"/>
@@ -30040,8 +30150,8 @@
         <v>32</v>
       </c>
       <c r="D15" s="81" t="str">
-        <f>VLOOKUP(C10,'Formato descripción HU'!B6:O22,3,0)</f>
-        <v>Soicitar los datos personales del cliente y generar automaticamente un recibo</v>
+        <f>VLOOKUP(C10,'Formato descripción HU'!B7:O23,3,0)</f>
+        <v>Solicitar los datos personales del cliente  y enviar su solicitud al correo del administrador</v>
       </c>
       <c r="E15" s="73"/>
       <c r="F15" s="42"/>
@@ -30049,8 +30159,8 @@
         <v>33</v>
       </c>
       <c r="H15" s="81" t="str">
-        <f>VLOOKUP(C10,'Formato descripción HU'!B6:O22,4,0)</f>
-        <v>Para entregar un comprobante de compra profesional al cliente al instante.</v>
+        <f>VLOOKUP(C10,'Formato descripción HU'!B7:O23,4,0)</f>
+        <v>Para que el cliente pueda apartar productos o pedir una cotizacion formal de forma remota.</v>
       </c>
       <c r="I15" s="79"/>
       <c r="J15" s="73"/>
@@ -30058,12 +30168,12 @@
       <c r="L15" s="83" t="s">
         <v>34</v>
       </c>
-      <c r="M15" s="86" t="str">
-        <f>VLOOKUP(C10,'Formato descripción HU'!B6:O22,6,0)</f>
-        <v>Diseñar un formato de ticket que tome los datos de la venta y los convierta en un archivo listo para imprimir.</v>
+      <c r="M15" s="109" t="str">
+        <f>VLOOKUP(C10,'Formato descripción HU'!B7:O23,6,0)</f>
+        <v>Crear un formulario sencillo donde el cliente deje su nombre, telefono y el pedido que desea realizar.</v>
       </c>
-      <c r="N15" s="79"/>
-      <c r="O15" s="73"/>
+      <c r="N15" s="110"/>
+      <c r="O15" s="111"/>
       <c r="P15" s="36"/>
       <c r="Q15" s="25"/>
       <c r="R15" s="25"/>
@@ -30089,9 +30199,9 @@
       <c r="J16" s="75"/>
       <c r="K16" s="42"/>
       <c r="L16" s="84"/>
-      <c r="M16" s="74"/>
-      <c r="N16" s="62"/>
-      <c r="O16" s="75"/>
+      <c r="M16" s="112"/>
+      <c r="N16" s="113"/>
+      <c r="O16" s="114"/>
       <c r="P16" s="36"/>
       <c r="Q16" s="25"/>
       <c r="R16" s="25"/>
@@ -30117,9 +30227,9 @@
       <c r="J17" s="77"/>
       <c r="K17" s="42"/>
       <c r="L17" s="85"/>
-      <c r="M17" s="76"/>
-      <c r="N17" s="80"/>
-      <c r="O17" s="77"/>
+      <c r="M17" s="115"/>
+      <c r="N17" s="116"/>
+      <c r="O17" s="117"/>
       <c r="P17" s="36"/>
       <c r="Q17" s="25"/>
       <c r="R17" s="25"/>
@@ -30162,24 +30272,24 @@
     </row>
     <row r="19" spans="1:26" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B19" s="32"/>
-      <c r="C19" s="93" t="s">
+      <c r="C19" s="92" t="s">
         <v>35</v>
       </c>
       <c r="D19" s="73"/>
-      <c r="E19" s="87" t="str">
-        <f>VLOOKUP(C10,'Formato descripción HU'!B6:O22,14,0)</f>
-        <v>Generador de recibos de venta.</v>
+      <c r="E19" s="86" t="str">
+        <f>VLOOKUP(C10,'Formato descripción HU'!B7:O23,14,0)</f>
+        <v>Formulario de pedidos y contacto.</v>
       </c>
-      <c r="F19" s="88"/>
-      <c r="G19" s="88"/>
-      <c r="H19" s="88"/>
-      <c r="I19" s="88"/>
-      <c r="J19" s="88"/>
-      <c r="K19" s="88"/>
-      <c r="L19" s="88"/>
-      <c r="M19" s="88"/>
-      <c r="N19" s="88"/>
-      <c r="O19" s="89"/>
+      <c r="F19" s="87"/>
+      <c r="G19" s="87"/>
+      <c r="H19" s="87"/>
+      <c r="I19" s="87"/>
+      <c r="J19" s="87"/>
+      <c r="K19" s="87"/>
+      <c r="L19" s="87"/>
+      <c r="M19" s="87"/>
+      <c r="N19" s="87"/>
+      <c r="O19" s="88"/>
       <c r="P19" s="36"/>
       <c r="Q19" s="25"/>
     </row>
@@ -30187,17 +30297,17 @@
       <c r="B20" s="32"/>
       <c r="C20" s="76"/>
       <c r="D20" s="77"/>
-      <c r="E20" s="90"/>
-      <c r="F20" s="91"/>
-      <c r="G20" s="91"/>
-      <c r="H20" s="91"/>
-      <c r="I20" s="91"/>
-      <c r="J20" s="91"/>
-      <c r="K20" s="91"/>
-      <c r="L20" s="91"/>
-      <c r="M20" s="91"/>
-      <c r="N20" s="91"/>
-      <c r="O20" s="92"/>
+      <c r="E20" s="89"/>
+      <c r="F20" s="90"/>
+      <c r="G20" s="90"/>
+      <c r="H20" s="90"/>
+      <c r="I20" s="90"/>
+      <c r="J20" s="90"/>
+      <c r="K20" s="90"/>
+      <c r="L20" s="90"/>
+      <c r="M20" s="90"/>
+      <c r="N20" s="90"/>
+      <c r="O20" s="91"/>
       <c r="P20" s="36"/>
       <c r="Q20" s="25"/>
     </row>
@@ -30227,8 +30337,8 @@
       </c>
       <c r="D22" s="73"/>
       <c r="E22" s="78" t="str">
-        <f>VLOOKUP(C10,'Formato descripción HU'!B6:O22,12,0)</f>
-        <v>Realizar una venta de prueba y confirmar que se genera un documento con el total correcto.</v>
+        <f>VLOOKUP(C10,'Formato descripción HU'!B7:O23,12,0)</f>
+        <v>Llenar el formulario como cliente y verificar que el dueño reciba un correo con los datos.</v>
       </c>
       <c r="F22" s="79"/>
       <c r="G22" s="79"/>
@@ -30239,8 +30349,8 @@
       </c>
       <c r="K22" s="73"/>
       <c r="L22" s="81" t="str">
-        <f>VLOOKUP(C10,'Formato descripción HU'!B6:O22,13,0)</f>
-        <v>Procesa los datos de los productos seleccionados y los datos del cliente para crear un documento legal o informativo que respalda la transacción comercial.</v>
+        <f>VLOOKUP(C10,'Formato descripción HU'!B7:O23,13,0)</f>
+        <v>Actua como una forma de comunicacion directa entre el cliente y el negocio registrando los datos del cliente y su pedido.</v>
       </c>
       <c r="M22" s="79"/>
       <c r="N22" s="79"/>
@@ -30914,12 +31024,12 @@
       <c r="E55" s="62"/>
       <c r="F55" s="25"/>
       <c r="G55" s="64"/>
-      <c r="H55" s="104"/>
+      <c r="H55" s="103"/>
       <c r="I55" s="62"/>
       <c r="J55" s="62"/>
       <c r="K55" s="25"/>
       <c r="L55" s="64"/>
-      <c r="M55" s="105"/>
+      <c r="M55" s="104"/>
       <c r="N55" s="62"/>
       <c r="O55" s="62"/>
       <c r="P55" s="25"/>
@@ -30981,9 +31091,9 @@
     <row r="59" spans="1:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A59" s="25"/>
       <c r="B59" s="25"/>
-      <c r="C59" s="102"/>
+      <c r="C59" s="101"/>
       <c r="D59" s="62"/>
-      <c r="E59" s="103"/>
+      <c r="E59" s="102"/>
       <c r="F59" s="62"/>
       <c r="G59" s="62"/>
       <c r="H59" s="62"/>
@@ -31037,14 +31147,14 @@
       <c r="B62" s="25"/>
       <c r="C62" s="64"/>
       <c r="D62" s="62"/>
-      <c r="E62" s="106"/>
+      <c r="E62" s="105"/>
       <c r="F62" s="62"/>
       <c r="G62" s="62"/>
       <c r="H62" s="62"/>
       <c r="I62" s="25"/>
       <c r="J62" s="64"/>
       <c r="K62" s="62"/>
-      <c r="L62" s="108"/>
+      <c r="L62" s="107"/>
       <c r="M62" s="62"/>
       <c r="N62" s="62"/>
       <c r="O62" s="62"/>
@@ -31253,16 +31363,16 @@
       <c r="A75" s="25"/>
       <c r="B75" s="25"/>
       <c r="C75" s="64"/>
-      <c r="D75" s="107"/>
+      <c r="D75" s="106"/>
       <c r="E75" s="62"/>
       <c r="F75" s="25"/>
       <c r="G75" s="64"/>
-      <c r="H75" s="104"/>
+      <c r="H75" s="103"/>
       <c r="I75" s="62"/>
       <c r="J75" s="62"/>
       <c r="K75" s="25"/>
       <c r="L75" s="64"/>
-      <c r="M75" s="105"/>
+      <c r="M75" s="104"/>
       <c r="N75" s="62"/>
       <c r="O75" s="62"/>
       <c r="P75" s="25"/>
@@ -31324,9 +31434,9 @@
     <row r="79" spans="1:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A79" s="25"/>
       <c r="B79" s="25"/>
-      <c r="C79" s="102"/>
+      <c r="C79" s="101"/>
       <c r="D79" s="62"/>
-      <c r="E79" s="103"/>
+      <c r="E79" s="102"/>
       <c r="F79" s="62"/>
       <c r="G79" s="62"/>
       <c r="H79" s="62"/>
@@ -31380,14 +31490,14 @@
       <c r="B82" s="25"/>
       <c r="C82" s="64"/>
       <c r="D82" s="62"/>
-      <c r="E82" s="106"/>
+      <c r="E82" s="105"/>
       <c r="F82" s="62"/>
       <c r="G82" s="62"/>
       <c r="H82" s="62"/>
       <c r="I82" s="25"/>
       <c r="J82" s="64"/>
       <c r="K82" s="62"/>
-      <c r="L82" s="100"/>
+      <c r="L82" s="99"/>
       <c r="M82" s="62"/>
       <c r="N82" s="62"/>
       <c r="O82" s="62"/>
@@ -31561,16 +31671,16 @@
       <c r="A93" s="25"/>
       <c r="B93" s="25"/>
       <c r="C93" s="64"/>
-      <c r="D93" s="104"/>
+      <c r="D93" s="103"/>
       <c r="E93" s="62"/>
       <c r="F93" s="25"/>
       <c r="G93" s="64"/>
-      <c r="H93" s="104"/>
+      <c r="H93" s="103"/>
       <c r="I93" s="62"/>
       <c r="J93" s="62"/>
       <c r="K93" s="25"/>
       <c r="L93" s="64"/>
-      <c r="M93" s="101"/>
+      <c r="M93" s="100"/>
       <c r="N93" s="62"/>
       <c r="O93" s="62"/>
       <c r="P93" s="25"/>
@@ -31632,9 +31742,9 @@
     <row r="97" spans="1:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A97" s="25"/>
       <c r="B97" s="25"/>
-      <c r="C97" s="102"/>
+      <c r="C97" s="101"/>
       <c r="D97" s="62"/>
-      <c r="E97" s="103"/>
+      <c r="E97" s="102"/>
       <c r="F97" s="62"/>
       <c r="G97" s="62"/>
       <c r="H97" s="62"/>
@@ -31688,14 +31798,14 @@
       <c r="B100" s="25"/>
       <c r="C100" s="64"/>
       <c r="D100" s="62"/>
-      <c r="E100" s="99"/>
+      <c r="E100" s="98"/>
       <c r="F100" s="62"/>
       <c r="G100" s="62"/>
       <c r="H100" s="62"/>
       <c r="I100" s="25"/>
       <c r="J100" s="64"/>
       <c r="K100" s="62"/>
-      <c r="L100" s="100"/>
+      <c r="L100" s="99"/>
       <c r="M100" s="62"/>
       <c r="N100" s="62"/>
       <c r="O100" s="62"/>
@@ -32821,7 +32931,7 @@
       <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" count="1">
         <x14:dataValidation type="list" allowBlank="1" showErrorMessage="1" xr:uid="{00000000-0002-0000-0100-000000000000}">
           <x14:formula1>
-            <xm:f>'Formato descripción HU'!$B$6:$B$22</xm:f>
+            <xm:f>'Formato descripción HU'!$B$7:$B$23</xm:f>
           </x14:formula1>
           <xm:sqref>C10:C11 C50:C51</xm:sqref>
         </x14:dataValidation>
